--- a/data/fmsForecastOutput/File1/RPT_RPT4636734643070GR_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT4636734643070GR_fmsForecastOutput.xlsx
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>525.7446861388845</v>
+        <v>525.7446861388844</v>
       </c>
       <c r="D8" s="149" t="n">
         <v>561.5268747781269</v>
@@ -1887,7 +1887,7 @@
         <v>637.3706521017883</v>
       </c>
       <c r="G8" s="150" t="n">
-        <v>678.7571483337661</v>
+        <v>678.7571483337658</v>
       </c>
       <c r="H8" s="148" t="n">
         <v>45.3147253789129</v>
@@ -1902,7 +1902,7 @@
         <v>65.39044139336183</v>
       </c>
       <c r="L8" s="150" t="n">
-        <v>75.03547156254466</v>
+        <v>75.03547156254464</v>
       </c>
       <c r="M8" s="151" t="n">
         <v>54216767.67339625</v>
@@ -1917,7 +1917,7 @@
         <v>81552007.84241547</v>
       </c>
       <c r="Q8" s="153" t="n">
-        <v>95046278.11887144</v>
+        <v>95046278.11887141</v>
       </c>
       <c r="S8" s="21" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>648.1260125742092</v>
       </c>
       <c r="X8" s="150" t="n">
-        <v>690.2108884447812</v>
+        <v>690.2108884447809</v>
       </c>
       <c r="Y8" s="148" t="n">
         <v>55.18193508189709</v>
@@ -1952,7 +1952,7 @@
         <v>79.34775647936618</v>
       </c>
       <c r="AC8" s="150" t="n">
-        <v>90.89573510807107</v>
+        <v>90.89573510807104</v>
       </c>
       <c r="AD8" s="151" t="n">
         <v>54216767.67339625</v>
@@ -1967,7 +1967,7 @@
         <v>81552007.84241547</v>
       </c>
       <c r="AH8" s="153" t="n">
-        <v>95046278.11887144</v>
+        <v>95046278.11887141</v>
       </c>
       <c r="AQ8" s="28" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>159.3176458849825</v>
       </c>
       <c r="M9" s="158" t="n">
-        <v>27075095.88191495</v>
+        <v>27075095.88191496</v>
       </c>
       <c r="N9" s="159" t="n">
         <v>29709194.45280086</v>
@@ -2081,7 +2081,7 @@
         <v>1835.586970626192</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>1936.477368027242</v>
+        <v>1936.477368027243</v>
       </c>
       <c r="X9" s="157" t="n">
         <v>2052.090569437423</v>
@@ -2102,7 +2102,7 @@
         <v>160.020030537208</v>
       </c>
       <c r="AD9" s="158" t="n">
-        <v>27075095.88191495</v>
+        <v>27075095.88191496</v>
       </c>
       <c r="AE9" s="159" t="n">
         <v>29709194.45280086</v>
@@ -2170,40 +2170,40 @@
         </is>
       </c>
       <c r="C10" s="161" t="n">
-        <v>674.915961658558</v>
+        <v>674.9159616585579</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>715.3415380202639</v>
+        <v>715.3415380202638</v>
       </c>
       <c r="E10" s="162" t="n">
         <v>764.6783632314653</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>806.621388744405</v>
+        <v>806.6213887444051</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>856.3504122896181</v>
+        <v>856.3504122896179</v>
       </c>
       <c r="H10" s="161" t="n">
         <v>55.61598365125351</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>62.01347043658532</v>
+        <v>62.01347043658531</v>
       </c>
       <c r="J10" s="162" t="n">
         <v>69.80399040697361</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>78.53514688418744</v>
+        <v>78.53514688418745</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>89.88622615389883</v>
+        <v>89.88622615389882</v>
       </c>
       <c r="M10" s="164" t="n">
         <v>81291863.5553112</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>91889013.83486563</v>
+        <v>91889013.83486561</v>
       </c>
       <c r="O10" s="165" t="n">
         <v>104693657.9881079</v>
@@ -2229,10 +2229,10 @@
         <v>777.463269024956</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>820.1087615790108</v>
+        <v>820.1087615790109</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>870.6702648551108</v>
+        <v>870.6702648551105</v>
       </c>
       <c r="Y10" s="161" t="n">
         <v>65.21071091640233</v>
@@ -2244,7 +2244,7 @@
         <v>81.75228062072243</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>91.90094707753259</v>
+        <v>91.90094707753261</v>
       </c>
       <c r="AC10" s="163" t="n">
         <v>105.0706821249251</v>
@@ -2253,7 +2253,7 @@
         <v>81291863.5553112</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>91889013.83486563</v>
+        <v>91889013.83486561</v>
       </c>
       <c r="AF10" s="165" t="n">
         <v>104693657.9881079</v>
@@ -2333,7 +2333,7 @@
         <v>2065.714141544101</v>
       </c>
       <c r="H11" s="155" t="n">
-        <v>163.1362207566319</v>
+        <v>163.136220756632</v>
       </c>
       <c r="I11" s="156" t="n">
         <v>182.2754307563951</v>
@@ -2345,7 +2345,7 @@
         <v>233.6586133253074</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>268.3575864222934</v>
+        <v>268.3575864222935</v>
       </c>
       <c r="M11" s="158" t="n">
         <v>10322723.77456103</v>
@@ -2368,13 +2368,13 @@
         </is>
       </c>
       <c r="T11" s="155" t="n">
-        <v>2005.546509294253</v>
+        <v>2005.546509294254</v>
       </c>
       <c r="U11" s="156" t="n">
         <v>2156.512507995119</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>2342.143825980947</v>
+        <v>2342.143825980948</v>
       </c>
       <c r="W11" s="156" t="n">
         <v>2511.677833338427</v>
@@ -2389,13 +2389,13 @@
         <v>209.6755471537865</v>
       </c>
       <c r="AA11" s="156" t="n">
-        <v>237.5151288471992</v>
+        <v>237.5151288471993</v>
       </c>
       <c r="AB11" s="156" t="n">
         <v>269.2110311756689</v>
       </c>
       <c r="AC11" s="157" t="n">
-        <v>309.5170540836088</v>
+        <v>309.5170540836089</v>
       </c>
       <c r="AD11" s="158" t="n">
         <v>10322723.77456103</v>
@@ -2467,13 +2467,13 @@
         <v>763.8817096615511</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>817.5294072259524</v>
+        <v>817.5294072259527</v>
       </c>
       <c r="F12" s="162" t="n">
         <v>863.4810932088999</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>917.8561006809391</v>
+        <v>917.8561006809389</v>
       </c>
       <c r="H12" s="161" t="n">
         <v>60.07748730676987</v>
@@ -2488,10 +2488,10 @@
         <v>84.9708057791732</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>97.29228259059225</v>
+        <v>97.29228259059224</v>
       </c>
       <c r="M12" s="164" t="n">
-        <v>91614587.32987222</v>
+        <v>91614587.32987224</v>
       </c>
       <c r="N12" s="165" t="n">
         <v>103572969.597549</v>
@@ -2503,7 +2503,7 @@
         <v>134425351.505289</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>156074940.2930978</v>
+        <v>156074940.2930977</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>741.1282678646601</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>786.0679014429325</v>
+        <v>786.0679014429323</v>
       </c>
       <c r="V12" s="162" t="n">
         <v>841.1790250669774</v>
@@ -2523,16 +2523,16 @@
         <v>888.3654199818526</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>944.1392633050568</v>
+        <v>944.1392633050566</v>
       </c>
       <c r="Y12" s="161" t="n">
         <v>70.38378063768404</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>78.45494342031293</v>
+        <v>78.45494342031294</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>88.31940133143677</v>
+        <v>88.31940133143678</v>
       </c>
       <c r="AB12" s="162" t="n">
         <v>99.36735825300117</v>
@@ -2541,7 +2541,7 @@
         <v>113.6642322783113</v>
       </c>
       <c r="AD12" s="164" t="n">
-        <v>91614587.32987222</v>
+        <v>91614587.32987224</v>
       </c>
       <c r="AE12" s="165" t="n">
         <v>103572969.597549</v>
@@ -2553,7 +2553,7 @@
         <v>134425351.505289</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>156074940.2930978</v>
+        <v>156074940.2930977</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2749,10 +2749,10 @@
         <v>720.1062821332659</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>763.8817096615512</v>
+        <v>763.8817096615511</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>817.5294072259524</v>
+        <v>817.5294072259526</v>
       </c>
       <c r="F14" s="168" t="n">
         <v>863.4810932088999</v>
@@ -2764,7 +2764,7 @@
         <v>60.07748730676987</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>67.00024842914529</v>
+        <v>67.00024842914527</v>
       </c>
       <c r="J14" s="168" t="n">
         <v>75.46585380382001</v>
@@ -2776,7 +2776,7 @@
         <v>97.29228259059224</v>
       </c>
       <c r="M14" s="170" t="n">
-        <v>91614587.32987222</v>
+        <v>91614587.32987224</v>
       </c>
       <c r="N14" s="171" t="n">
         <v>103572969.597549</v>
@@ -2799,7 +2799,7 @@
         <v>741.1282678646601</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>786.0679014429327</v>
+        <v>786.0679014429323</v>
       </c>
       <c r="V14" s="168" t="n">
         <v>841.1790250669773</v>
@@ -2808,13 +2808,13 @@
         <v>888.3654199818526</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>944.1392633050567</v>
+        <v>944.1392633050566</v>
       </c>
       <c r="Y14" s="167" t="n">
         <v>70.38378063768404</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>78.45494342031294</v>
+        <v>78.45494342031293</v>
       </c>
       <c r="AA14" s="168" t="n">
         <v>88.31940133143675</v>
@@ -2826,7 +2826,7 @@
         <v>113.6642322783113</v>
       </c>
       <c r="AD14" s="170" t="n">
-        <v>91614587.32987222</v>
+        <v>91614587.32987224</v>
       </c>
       <c r="AE14" s="171" t="n">
         <v>103572969.597549</v>
@@ -3572,7 +3572,7 @@
         <v>7132.963641496925</v>
       </c>
       <c r="E22" s="80" t="n">
-        <v>7525.734884119331</v>
+        <v>7525.734884119332</v>
       </c>
       <c r="F22" s="80" t="n">
         <v>8038.535062615124</v>
@@ -3709,7 +3709,7 @@
         <v>135587.7072163942</v>
       </c>
       <c r="E23" s="86" t="n">
-        <v>144437.7530896319</v>
+        <v>144437.7530896318</v>
       </c>
       <c r="F23" s="86" t="n">
         <v>155678.3959284303</v>
@@ -3948,7 +3948,7 @@
         <v>135587.7072163942</v>
       </c>
       <c r="E25" s="92" t="n">
-        <v>144437.7530896319</v>
+        <v>144437.7530896318</v>
       </c>
       <c r="F25" s="92" t="n">
         <v>155678.3959284303</v>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>540.56924056598</v>
+        <v>540.5692405659798</v>
       </c>
       <c r="D35" s="149" t="n">
         <v>590.9387062588254</v>
@@ -4420,7 +4420,7 @@
         <v>683.5994754926789</v>
       </c>
       <c r="G35" s="150" t="n">
-        <v>729.8190325574336</v>
+        <v>729.8190325574334</v>
       </c>
       <c r="H35" s="148" t="n">
         <v>46.59247602564243</v>
@@ -4435,7 +4435,7 @@
         <v>70.13324396304046</v>
       </c>
       <c r="L35" s="150" t="n">
-        <v>80.68027776606019</v>
+        <v>80.68027776606016</v>
       </c>
       <c r="M35" s="151" t="n">
         <v>55745531.43349849</v>
@@ -4470,7 +4470,7 @@
         <v>695.134927828673</v>
       </c>
       <c r="X35" s="150" t="n">
-        <v>742.1344203916622</v>
+        <v>742.1344203916619</v>
       </c>
       <c r="Y35" s="148" t="n">
         <v>56.73791390884794</v>
@@ -4485,7 +4485,7 @@
         <v>85.10289033852952</v>
       </c>
       <c r="AC35" s="150" t="n">
-        <v>97.7336851965631</v>
+        <v>97.73368519656307</v>
       </c>
       <c r="AD35" s="151" t="n">
         <v>55745531.43349849</v>
@@ -4519,13 +4519,13 @@
         <v>1914.652247498776</v>
       </c>
       <c r="F36" s="156" t="n">
-        <v>2045.518265308115</v>
+        <v>2045.518265308116</v>
       </c>
       <c r="G36" s="157" t="n">
         <v>2173.120521689797</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>105.0017260455565</v>
+        <v>105.0017260455566</v>
       </c>
       <c r="I36" s="156" t="n">
         <v>117.2526367445623</v>
@@ -4549,7 +4549,7 @@
         <v>35299270.64889549</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>40274580.71405576</v>
+        <v>40274580.71405577</v>
       </c>
       <c r="Q36" s="160" t="n">
         <v>46428786.46876388</v>
@@ -4569,7 +4569,7 @@
         <v>1944.75588636775</v>
       </c>
       <c r="W36" s="156" t="n">
-        <v>2077.67948060931</v>
+        <v>2077.679480609311</v>
       </c>
       <c r="X36" s="157" t="n">
         <v>2207.287998049625</v>
@@ -4584,7 +4584,7 @@
         <v>132.2204869999946</v>
       </c>
       <c r="AB36" s="156" t="n">
-        <v>150.2411103502221</v>
+        <v>150.2411103502222</v>
       </c>
       <c r="AC36" s="157" t="n">
         <v>172.1221753624382</v>
@@ -4599,7 +4599,7 @@
         <v>35299270.64889549</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>40274580.71405576</v>
+        <v>40274580.71405577</v>
       </c>
       <c r="AH36" s="160" t="n">
         <v>46428786.46876388</v>
@@ -4621,10 +4621,10 @@
         <v>809.958282950766</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>865.2243178712511</v>
+        <v>865.2243178712512</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>920.8794661320745</v>
+        <v>920.8794661320744</v>
       </c>
       <c r="H37" s="161" t="n">
         <v>57.19065829931702</v>
@@ -4636,10 +4636,10 @@
         <v>73.93738718357088</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>84.24090885757698</v>
+        <v>84.240908857577</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>96.65947346474206</v>
+        <v>96.65947346474205</v>
       </c>
       <c r="M37" s="164" t="n">
         <v>83593508.30256727</v>
@@ -4671,10 +4671,10 @@
         <v>823.5002384213285</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>879.6915798649629</v>
+        <v>879.691579864963</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>936.2783705949605</v>
+        <v>936.2783705949603</v>
       </c>
       <c r="Y37" s="161" t="n">
         <v>67.05704440761882</v>
@@ -4686,7 +4686,7 @@
         <v>86.59318744033327</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>98.57776567350122</v>
+        <v>98.57776567350123</v>
       </c>
       <c r="AC37" s="163" t="n">
         <v>112.9881322794418</v>
@@ -4741,7 +4741,7 @@
         <v>250.6700069020689</v>
       </c>
       <c r="L38" s="157" t="n">
-        <v>288.6233076017104</v>
+        <v>288.6233076017105</v>
       </c>
       <c r="M38" s="158" t="n">
         <v>10616235.42155413</v>
@@ -4776,10 +4776,10 @@
         <v>2694.539229085313</v>
       </c>
       <c r="X38" s="157" t="n">
-        <v>2924.959334771552</v>
+        <v>2924.959334771553</v>
       </c>
       <c r="Y38" s="155" t="n">
-        <v>192.8803621630839</v>
+        <v>192.880362163084</v>
       </c>
       <c r="Z38" s="156" t="n">
         <v>220.7106826995256</v>
@@ -4791,7 +4791,7 @@
         <v>288.8108000066136</v>
       </c>
       <c r="AC38" s="157" t="n">
-        <v>332.8910395257876</v>
+        <v>332.8910395257877</v>
       </c>
       <c r="AD38" s="158" t="n">
         <v>10616235.42155413</v>
@@ -4819,16 +4819,16 @@
         <v>740.504654020139</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>803.9939146639027</v>
+        <v>803.9939146639028</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>865.952492491571</v>
+        <v>865.9524924915713</v>
       </c>
       <c r="F39" s="162" t="n">
         <v>926.2300002366524</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>987.0370608328329</v>
+        <v>987.0370608328327</v>
       </c>
       <c r="H39" s="161" t="n">
         <v>61.77929571827543</v>
@@ -4837,7 +4837,7 @@
         <v>70.51849957484833</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>79.93577187781914</v>
+        <v>79.93577187781915</v>
       </c>
       <c r="K39" s="162" t="n">
         <v>91.14560825469265</v>
@@ -4846,19 +4846,19 @@
         <v>104.6254293877788</v>
       </c>
       <c r="M39" s="164" t="n">
-        <v>94209743.72412139</v>
+        <v>94209743.72412141</v>
       </c>
       <c r="N39" s="165" t="n">
         <v>109011691.5052119</v>
       </c>
       <c r="O39" s="165" t="n">
-        <v>125076232.2978488</v>
+        <v>125076232.2978489</v>
       </c>
       <c r="P39" s="165" t="n">
         <v>144194000.6976317</v>
       </c>
       <c r="Q39" s="166" t="n">
-        <v>167838673.4285159</v>
+        <v>167838673.4285158</v>
       </c>
       <c r="S39" s="42" t="inlineStr">
         <is>
@@ -4869,25 +4869,25 @@
         <v>762.1221272419064</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>827.3451259263117</v>
+        <v>827.3451259263115</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>891.0029008743099</v>
+        <v>891.0029008743101</v>
       </c>
       <c r="W39" s="162" t="n">
         <v>952.9226634276282</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>1015.301246870987</v>
+        <v>1015.301246870986</v>
       </c>
       <c r="Y39" s="161" t="n">
         <v>72.37753429304497</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>82.57469224283392</v>
+        <v>82.57469224283393</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>93.550647893921</v>
+        <v>93.55064789392101</v>
       </c>
       <c r="AB39" s="162" t="n">
         <v>106.5883537949412</v>
@@ -4896,19 +4896,19 @@
         <v>122.2313711992247</v>
       </c>
       <c r="AD39" s="164" t="n">
-        <v>94209743.72412139</v>
+        <v>94209743.72412141</v>
       </c>
       <c r="AE39" s="165" t="n">
         <v>109011691.5052119</v>
       </c>
       <c r="AF39" s="165" t="n">
-        <v>125076232.2978488</v>
+        <v>125076232.2978489</v>
       </c>
       <c r="AG39" s="165" t="n">
         <v>144194000.6976317</v>
       </c>
       <c r="AH39" s="166" t="n">
-        <v>167838673.4285159</v>
+        <v>167838673.4285158</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -5023,16 +5023,16 @@
         <v>740.504654020139</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>803.9939146639027</v>
+        <v>803.9939146639028</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>865.952492491571</v>
+        <v>865.9524924915713</v>
       </c>
       <c r="F41" s="180" t="n">
         <v>926.2300002366524</v>
       </c>
       <c r="G41" s="181" t="n">
-        <v>987.0370608328329</v>
+        <v>987.0370608328327</v>
       </c>
       <c r="H41" s="179" t="n">
         <v>61.77929571827543</v>
@@ -5041,7 +5041,7 @@
         <v>70.51849957484833</v>
       </c>
       <c r="J41" s="180" t="n">
-        <v>79.93577187781914</v>
+        <v>79.93577187781915</v>
       </c>
       <c r="K41" s="180" t="n">
         <v>91.14560825469265</v>
@@ -5050,19 +5050,19 @@
         <v>104.6254293877788</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>94209743.72412139</v>
+        <v>94209743.72412141</v>
       </c>
       <c r="N41" s="183" t="n">
         <v>109011691.5052119</v>
       </c>
       <c r="O41" s="183" t="n">
-        <v>125076232.2978488</v>
+        <v>125076232.2978489</v>
       </c>
       <c r="P41" s="183" t="n">
         <v>144194000.6976317</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>167838673.4285159</v>
+        <v>167838673.4285158</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5073,25 +5073,25 @@
         <v>762.1221272419064</v>
       </c>
       <c r="U41" s="186" t="n">
-        <v>827.3451259263117</v>
+        <v>827.3451259263115</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>891.0029008743099</v>
+        <v>891.0029008743101</v>
       </c>
       <c r="W41" s="186" t="n">
         <v>952.9226634276282</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>1015.301246870987</v>
+        <v>1015.301246870986</v>
       </c>
       <c r="Y41" s="185" t="n">
         <v>72.37753429304497</v>
       </c>
       <c r="Z41" s="186" t="n">
-        <v>82.57469224283392</v>
+        <v>82.57469224283393</v>
       </c>
       <c r="AA41" s="186" t="n">
-        <v>93.550647893921</v>
+        <v>93.55064789392101</v>
       </c>
       <c r="AB41" s="186" t="n">
         <v>106.5883537949412</v>
@@ -5100,19 +5100,19 @@
         <v>122.2313711992247</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>94209743.72412139</v>
+        <v>94209743.72412141</v>
       </c>
       <c r="AE41" s="189" t="n">
         <v>109011691.5052119</v>
       </c>
       <c r="AF41" s="189" t="n">
-        <v>125076232.2978488</v>
+        <v>125076232.2978489</v>
       </c>
       <c r="AG41" s="189" t="n">
         <v>144194000.6976317</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>167838673.4285159</v>
+        <v>167838673.4285158</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -5374,7 +5374,7 @@
         <v>0.181917220935476</v>
       </c>
       <c r="D46" s="149" t="n">
-        <v>0.2017575055825044</v>
+        <v>0.2017575055825043</v>
       </c>
       <c r="E46" s="149" t="n">
         <v>0.2252303983415999</v>
@@ -5392,7 +5392,7 @@
         <v>0.01838764150491236</v>
       </c>
       <c r="J46" s="149" t="n">
-        <v>0.02166450926127892</v>
+        <v>0.02166450926127891</v>
       </c>
       <c r="K46" s="149" t="n">
         <v>0.02557704780861915</v>
@@ -5407,7 +5407,7 @@
         <v>22341.30870593323</v>
       </c>
       <c r="O46" s="152" t="n">
-        <v>26684.31351095444</v>
+        <v>26684.31351095443</v>
       </c>
       <c r="P46" s="152" t="n">
         <v>31898.53989402941</v>
@@ -5424,7 +5424,7 @@
         <v>0.184986997180821</v>
       </c>
       <c r="U46" s="149" t="n">
-        <v>0.205162078248975</v>
+        <v>0.2051620782489749</v>
       </c>
       <c r="V46" s="149" t="n">
         <v>0.229031066156352</v>
@@ -5457,7 +5457,7 @@
         <v>22341.30870593323</v>
       </c>
       <c r="AF46" s="152" t="n">
-        <v>26684.31351095444</v>
+        <v>26684.31351095443</v>
       </c>
       <c r="AG46" s="152" t="n">
         <v>31898.53989402941</v>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="C48" s="161" t="n">
-        <v>0.1615583391258172</v>
+        <v>0.1615583391258171</v>
       </c>
       <c r="D48" s="162" t="n">
         <v>0.1796400717568933</v>
@@ -5608,7 +5608,7 @@
         <v>19459.27968300569</v>
       </c>
       <c r="N48" s="165" t="n">
-        <v>23075.61935330788</v>
+        <v>23075.61935330787</v>
       </c>
       <c r="O48" s="165" t="n">
         <v>27456.33676105838</v>
@@ -5658,7 +5658,7 @@
         <v>19459.27968300569</v>
       </c>
       <c r="AE48" s="165" t="n">
-        <v>23075.61935330788</v>
+        <v>23075.61935330787</v>
       </c>
       <c r="AF48" s="165" t="n">
         <v>27456.33676105838</v>
@@ -5680,7 +5680,7 @@
         <v>0.1994285554806573</v>
       </c>
       <c r="D49" s="156" t="n">
-        <v>0.2079983300143855</v>
+        <v>0.2079983300143856</v>
       </c>
       <c r="E49" s="156" t="n">
         <v>0.2178794034705015</v>
@@ -5689,10 +5689,10 @@
         <v>0.2265826015246186</v>
       </c>
       <c r="G49" s="157" t="n">
-        <v>0.235224249840784</v>
+        <v>0.2352242498407841</v>
       </c>
       <c r="H49" s="155" t="n">
-        <v>0.02135684474724433</v>
+        <v>0.02135684474724434</v>
       </c>
       <c r="I49" s="156" t="n">
         <v>0.02314558103992517</v>
@@ -5701,22 +5701,22 @@
         <v>0.0252706175829999</v>
       </c>
       <c r="K49" s="156" t="n">
-        <v>0.02775086398713267</v>
+        <v>0.02775086398713268</v>
       </c>
       <c r="L49" s="157" t="n">
-        <v>0.03055805771271074</v>
+        <v>0.03055805771271075</v>
       </c>
       <c r="M49" s="158" t="n">
-        <v>1351.390929613805</v>
+        <v>1351.390929613806</v>
       </c>
       <c r="N49" s="159" t="n">
         <v>1483.644525484691</v>
       </c>
       <c r="O49" s="159" t="n">
-        <v>1639.702627229063</v>
+        <v>1639.702627229064</v>
       </c>
       <c r="P49" s="159" t="n">
-        <v>1821.392186934197</v>
+        <v>1821.392186934198</v>
       </c>
       <c r="Q49" s="160" t="n">
         <v>2034.225130062324</v>
@@ -5742,7 +5742,7 @@
         <v>0.3096807284968951</v>
       </c>
       <c r="Y49" s="155" t="n">
-        <v>0.024552655586236</v>
+        <v>0.02455265558623601</v>
       </c>
       <c r="Z49" s="156" t="n">
         <v>0.02662488492606867</v>
@@ -5757,16 +5757,16 @@
         <v>0.03524491380270291</v>
       </c>
       <c r="AD49" s="158" t="n">
-        <v>1351.390929613805</v>
+        <v>1351.390929613806</v>
       </c>
       <c r="AE49" s="159" t="n">
         <v>1483.644525484691</v>
       </c>
       <c r="AF49" s="159" t="n">
-        <v>1639.702627229063</v>
+        <v>1639.702627229064</v>
       </c>
       <c r="AG49" s="159" t="n">
-        <v>1821.392186934197</v>
+        <v>1821.392186934198</v>
       </c>
       <c r="AH49" s="160" t="n">
         <v>2034.225130062324</v>
@@ -5812,10 +5812,10 @@
         <v>20810.67061261949</v>
       </c>
       <c r="N50" s="165" t="n">
-        <v>24559.26387879257</v>
+        <v>24559.26387879256</v>
       </c>
       <c r="O50" s="165" t="n">
-        <v>29096.03938828745</v>
+        <v>29096.03938828744</v>
       </c>
       <c r="P50" s="165" t="n">
         <v>34530.54461000481</v>
@@ -5841,7 +5841,7 @@
         <v>0.2281990816550855</v>
       </c>
       <c r="X50" s="163" t="n">
-        <v>0.2486464670346972</v>
+        <v>0.2486464670346971</v>
       </c>
       <c r="Y50" s="161" t="n">
         <v>0.01598799621339462</v>
@@ -5862,10 +5862,10 @@
         <v>20810.67061261949</v>
       </c>
       <c r="AE50" s="165" t="n">
-        <v>24559.26387879257</v>
+        <v>24559.26387879256</v>
       </c>
       <c r="AF50" s="165" t="n">
-        <v>29096.03938828745</v>
+        <v>29096.03938828744</v>
       </c>
       <c r="AG50" s="165" t="n">
         <v>34530.54461000481</v>
@@ -6016,10 +6016,10 @@
         <v>20810.67061261949</v>
       </c>
       <c r="N52" s="183" t="n">
-        <v>24559.26387879257</v>
+        <v>24559.26387879256</v>
       </c>
       <c r="O52" s="183" t="n">
-        <v>29096.03938828745</v>
+        <v>29096.03938828744</v>
       </c>
       <c r="P52" s="183" t="n">
         <v>34530.54461000481</v>
@@ -6045,7 +6045,7 @@
         <v>0.2281990816550855</v>
       </c>
       <c r="X52" s="187" t="n">
-        <v>0.2486464670346972</v>
+        <v>0.2486464670346971</v>
       </c>
       <c r="Y52" s="185" t="n">
         <v>0.01598799621339462</v>
@@ -6066,10 +6066,10 @@
         <v>20810.67061261949</v>
       </c>
       <c r="AE52" s="189" t="n">
-        <v>24559.26387879257</v>
+        <v>24559.26387879256</v>
       </c>
       <c r="AF52" s="189" t="n">
-        <v>29096.03938828745</v>
+        <v>29096.03938828744</v>
       </c>
       <c r="AG52" s="189" t="n">
         <v>34530.54461000481</v>
@@ -6337,43 +6337,43 @@
         <v>0.01034250027988828</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.009529046918664097</v>
+        <v>0.009529046918664085</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.008814070349602288</v>
+        <v>0.008814070349602281</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.0003206394028269369</v>
+        <v>0.0003206394028269365</v>
       </c>
       <c r="G57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.0008914356574032223</v>
+        <v>0.000891435657403222</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.0008684519473910433</v>
+        <v>0.0008684519473910421</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.0008478096656780361</v>
+        <v>0.0008478096656780353</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>3.289569736199424e-05</v>
+        <v>3.289569736199421e-05</v>
       </c>
       <c r="L57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="M57" s="151" t="n">
-        <v>1066.557493818607</v>
+        <v>1066.557493818606</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>1055.184431768954</v>
+        <v>1055.184431768953</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>1044.252544275479</v>
+        <v>1044.252544275478</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>41.02602937192313</v>
+        <v>41.02602937192309</v>
       </c>
       <c r="Q57" s="153" t="n">
         <v>0</v>
@@ -6387,13 +6387,13 @@
         <v>0.01051702560252354</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.009689845559503425</v>
+        <v>0.009689845559503413</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.008962804062908107</v>
+        <v>0.008962804062908098</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.000326050057283168</v>
+        <v>0.0003260500572831677</v>
       </c>
       <c r="X57" s="150" t="n">
         <v>0</v>
@@ -6402,28 +6402,28 @@
         <v>0.001085544360363791</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.001056426501694552</v>
+        <v>0.001056426501694551</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>0.001030192616305478</v>
+        <v>0.001030192616305477</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>3.991714580723758e-05</v>
+        <v>3.991714580723754e-05</v>
       </c>
       <c r="AC57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="AD57" s="151" t="n">
-        <v>1066.557493818607</v>
+        <v>1066.557493818606</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>1055.184431768954</v>
+        <v>1055.184431768953</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>1044.252544275479</v>
+        <v>1044.252544275478</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>41.02602937192313</v>
+        <v>41.02602937192309</v>
       </c>
       <c r="AH57" s="153" t="n">
         <v>0</v>
@@ -6538,46 +6538,46 @@
         </is>
       </c>
       <c r="C59" s="161" t="n">
-        <v>0.008854965861558184</v>
+        <v>0.008854965861558178</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.008214445044247934</v>
+        <v>0.008214445044247922</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.007627179541740432</v>
+        <v>0.007627179541740426</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.000277879084492028</v>
+        <v>0.0002778790844920277</v>
       </c>
       <c r="G59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="H59" s="161" t="n">
-        <v>0.000729687345634261</v>
+        <v>0.0007296873456342607</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.0007121161261154022</v>
+        <v>0.0007121161261154013</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.0006962503363034959</v>
+        <v>0.0006962503363034954</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>2.705516494001639e-05</v>
+        <v>2.705516494001636e-05</v>
       </c>
       <c r="L59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="M59" s="164" t="n">
-        <v>1066.557493818607</v>
+        <v>1066.557493818606</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>1055.184431768954</v>
+        <v>1055.184431768953</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>1044.252544275479</v>
+        <v>1044.252544275478</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>41.02602937192313</v>
+        <v>41.02602937192309</v>
       </c>
       <c r="Q59" s="166" t="n">
         <v>0</v>
@@ -6588,46 +6588,46 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.009002921320424568</v>
+        <v>0.009002921320424564</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.008351753781564416</v>
+        <v>0.008351753781564405</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.007754700832520925</v>
+        <v>0.007754700832520918</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>0.0002825254512606019</v>
+        <v>0.0002825254512606016</v>
       </c>
       <c r="X59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.000855571140373785</v>
+        <v>0.0008555711403737846</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.0008345108556951465</v>
+        <v>0.0008345108556951454</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.0008154269196345153</v>
+        <v>0.0008154269196345147</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>3.165965023269067e-05</v>
+        <v>3.165965023269064e-05</v>
       </c>
       <c r="AC59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="AD59" s="164" t="n">
-        <v>1066.557493818607</v>
+        <v>1066.557493818606</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>1055.184431768954</v>
+        <v>1055.184431768953</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>1044.252544275479</v>
+        <v>1044.252544275478</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>41.02602937192313</v>
+        <v>41.02602937192309</v>
       </c>
       <c r="AH59" s="166" t="n">
         <v>0</v>
@@ -6742,46 +6742,46 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.008383323812720622</v>
+        <v>0.008383323812720618</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.007782301607069063</v>
+        <v>0.007782301607069052</v>
       </c>
       <c r="E61" s="162" t="n">
-        <v>0.007229775608787409</v>
+        <v>0.007229775608787405</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.0002635306532242529</v>
+        <v>0.0002635306532242527</v>
       </c>
       <c r="G61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.0006994092989374272</v>
+        <v>0.000699409298937427</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.0006825875452040666</v>
+        <v>0.0006825875452040657</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.0006673780591924062</v>
+        <v>0.0006673780591924056</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>2.59327183051121e-05</v>
+        <v>2.593271830511207e-05</v>
       </c>
       <c r="L61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="M61" s="164" t="n">
-        <v>1066.557493818607</v>
+        <v>1066.557493818606</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>1055.184431768954</v>
+        <v>1055.184431768953</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>1044.252544275479</v>
+        <v>1044.252544275478</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>41.02602937192313</v>
+        <v>41.02602937192309</v>
       </c>
       <c r="Q61" s="166" t="n">
         <v>0</v>
@@ -6792,46 +6792,46 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.008628057288799442</v>
+        <v>0.008628057288799437</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.008008330891146942</v>
+        <v>0.00800833089114693</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.00743891968203165</v>
+        <v>0.007438919682031643</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>0.0002711252409240851</v>
+        <v>0.0002711252409240849</v>
       </c>
       <c r="X61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="Y61" s="161" t="n">
-        <v>0.000819392968634044</v>
+        <v>0.0008193929686340435</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.0007992860995885491</v>
+        <v>0.0007992860995885481</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.0007810476881747791</v>
+        <v>0.0007810476881747783</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>3.032648315699318e-05</v>
+        <v>3.032648315699315e-05</v>
       </c>
       <c r="AC61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="AD61" s="164" t="n">
-        <v>1066.557493818607</v>
+        <v>1066.557493818606</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>1055.184431768954</v>
+        <v>1055.184431768953</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>1044.252544275479</v>
+        <v>1044.252544275478</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>41.02602937192313</v>
+        <v>41.02602937192309</v>
       </c>
       <c r="AH61" s="166" t="n">
         <v>0</v>
@@ -6946,46 +6946,46 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.008383323812720622</v>
+        <v>0.008383323812720618</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.007782301607069063</v>
+        <v>0.007782301607069052</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.007229775608787409</v>
+        <v>0.007229775608787405</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>0.0002635306532242529</v>
+        <v>0.0002635306532242527</v>
       </c>
       <c r="G63" s="181" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.0006994092989374272</v>
+        <v>0.000699409298937427</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.0006825875452040666</v>
+        <v>0.0006825875452040657</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.0006673780591924062</v>
+        <v>0.0006673780591924056</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>2.59327183051121e-05</v>
+        <v>2.593271830511207e-05</v>
       </c>
       <c r="L63" s="181" t="n">
         <v>0</v>
       </c>
       <c r="M63" s="182" t="n">
-        <v>1066.557493818607</v>
+        <v>1066.557493818606</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>1055.184431768954</v>
+        <v>1055.184431768953</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>1044.252544275479</v>
+        <v>1044.252544275478</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>41.02602937192313</v>
+        <v>41.02602937192309</v>
       </c>
       <c r="Q63" s="184" t="n">
         <v>0</v>
@@ -6996,46 +6996,46 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.008628057288799442</v>
+        <v>0.008628057288799437</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.008008330891146942</v>
+        <v>0.00800833089114693</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.00743891968203165</v>
+        <v>0.007438919682031643</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>0.0002711252409240851</v>
+        <v>0.0002711252409240849</v>
       </c>
       <c r="X63" s="187" t="n">
         <v>0</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.000819392968634044</v>
+        <v>0.0008193929686340435</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.0007992860995885491</v>
+        <v>0.0007992860995885481</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.0007810476881747791</v>
+        <v>0.0007810476881747783</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>3.032648315699318e-05</v>
+        <v>3.032648315699315e-05</v>
       </c>
       <c r="AC63" s="187" t="n">
         <v>0</v>
       </c>
       <c r="AD63" s="188" t="n">
-        <v>1066.557493818607</v>
+        <v>1066.557493818606</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>1055.184431768954</v>
+        <v>1055.184431768953</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>1044.252544275479</v>
+        <v>1044.252544275478</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>41.02602937192313</v>
+        <v>41.02602937192309</v>
       </c>
       <c r="AH63" s="190" t="n">
         <v>0</v>
@@ -7297,31 +7297,31 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.004389790632988983</v>
+        <v>0.004389790632988982</v>
       </c>
       <c r="D68" s="149" t="n">
-        <v>0.006387224154446735</v>
+        <v>0.006387224154446726</v>
       </c>
       <c r="E68" s="149" t="n">
-        <v>0.008442347676483792</v>
+        <v>0.008442347676483787</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.01031668646141136</v>
+        <v>0.01031668646141135</v>
       </c>
       <c r="G68" s="150" t="n">
-        <v>0.01204674054031116</v>
+        <v>0.01204674054031117</v>
       </c>
       <c r="H68" s="148" t="n">
         <v>0.0003783626582433422</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.0005821145915954861</v>
+        <v>0.0005821145915954854</v>
       </c>
       <c r="J68" s="149" t="n">
-        <v>0.0008120543264622833</v>
+        <v>0.0008120543264622828</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.001058430725048309</v>
+        <v>0.001058430725048308</v>
       </c>
       <c r="L68" s="150" t="n">
         <v>0.001331747090182217</v>
@@ -7330,16 +7330,16 @@
         <v>452.6917059904299</v>
       </c>
       <c r="N68" s="152" t="n">
-        <v>707.2794947404533</v>
+        <v>707.2794947404523</v>
       </c>
       <c r="O68" s="152" t="n">
-        <v>1000.212466108144</v>
+        <v>1000.212466108143</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>1320.027039893261</v>
+        <v>1320.02703989326</v>
       </c>
       <c r="Q68" s="153" t="n">
-        <v>1686.903562829613</v>
+        <v>1686.903562829614</v>
       </c>
       <c r="S68" s="21" t="inlineStr">
         <is>
@@ -7347,49 +7347,49 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.004463866495284433</v>
+        <v>0.004463866495284431</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.006495005863524011</v>
+        <v>0.006495005863524001</v>
       </c>
       <c r="V68" s="149" t="n">
-        <v>0.008584808726729305</v>
+        <v>0.008584808726729299</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.01049077618676587</v>
+        <v>0.01049077618676586</v>
       </c>
       <c r="X68" s="150" t="n">
-        <v>0.01225002419731908</v>
+        <v>0.01225002419731909</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.0004607505280019642</v>
+        <v>0.0004607505280019641</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.0007081120416990325</v>
+        <v>0.0007081120416990314</v>
       </c>
       <c r="AA68" s="149" t="n">
-        <v>0.0009867454984619846</v>
+        <v>0.0009867454984619837</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.001284348318069893</v>
+        <v>0.001284348318069892</v>
       </c>
       <c r="AC68" s="150" t="n">
-        <v>0.001613238755209897</v>
+        <v>0.001613238755209898</v>
       </c>
       <c r="AD68" s="151" t="n">
         <v>452.6917059904299</v>
       </c>
       <c r="AE68" s="152" t="n">
-        <v>707.2794947404533</v>
+        <v>707.2794947404523</v>
       </c>
       <c r="AF68" s="152" t="n">
-        <v>1000.212466108144</v>
+        <v>1000.212466108143</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>1320.027039893261</v>
+        <v>1320.02703989326</v>
       </c>
       <c r="AH68" s="153" t="n">
-        <v>1686.903562829613</v>
+        <v>1686.903562829614</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -7501,49 +7501,49 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>0.003758418674650035</v>
+        <v>0.003758418674650034</v>
       </c>
       <c r="D70" s="162" t="n">
-        <v>0.005506059761257975</v>
+        <v>0.005506059761257967</v>
       </c>
       <c r="E70" s="162" t="n">
-        <v>0.007305512541687682</v>
+        <v>0.007305512541687677</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.008940858059281078</v>
+        <v>0.008940858059281067</v>
       </c>
       <c r="G70" s="163" t="n">
-        <v>0.01045202489141601</v>
+        <v>0.01045202489141602</v>
       </c>
       <c r="H70" s="161" t="n">
         <v>0.0003097098949182212</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.0004773242655135329</v>
+        <v>0.0004773242655135322</v>
       </c>
       <c r="J70" s="162" t="n">
-        <v>0.000666886827061473</v>
+        <v>0.0006668868270614725</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.0008705095237423817</v>
+        <v>0.0008705095237423808</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>0.001097089532127489</v>
+        <v>0.00109708953212749</v>
       </c>
       <c r="M70" s="164" t="n">
         <v>452.6917059904299</v>
       </c>
       <c r="N70" s="165" t="n">
-        <v>707.2794947404533</v>
+        <v>707.2794947404523</v>
       </c>
       <c r="O70" s="165" t="n">
-        <v>1000.212466108144</v>
+        <v>1000.212466108143</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>1320.027039893261</v>
+        <v>1320.02703989326</v>
       </c>
       <c r="Q70" s="166" t="n">
-        <v>1686.903562829613</v>
+        <v>1686.903562829614</v>
       </c>
       <c r="S70" s="42" t="inlineStr">
         <is>
@@ -7551,31 +7551,31 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>0.003821217173064797</v>
+        <v>0.003821217173064796</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.005598096424639979</v>
+        <v>0.005598096424639971</v>
       </c>
       <c r="V70" s="162" t="n">
-        <v>0.007427655777471077</v>
+        <v>0.007427655777471073</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.009090356557324283</v>
+        <v>0.009090356557324274</v>
       </c>
       <c r="X70" s="163" t="n">
-        <v>0.01062680317529137</v>
+        <v>0.01062680317529138</v>
       </c>
       <c r="Y70" s="161" t="n">
         <v>0.000363140253926018</v>
       </c>
       <c r="Z70" s="162" t="n">
-        <v>0.0005593642197525573</v>
+        <v>0.0005593642197525566</v>
       </c>
       <c r="AA70" s="162" t="n">
-        <v>0.0007810372832603287</v>
+        <v>0.0007810372832603281</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.001018660470450388</v>
+        <v>0.001018660470450387</v>
       </c>
       <c r="AC70" s="163" t="n">
         <v>0.001282420571260687</v>
@@ -7584,16 +7584,16 @@
         <v>452.6917059904299</v>
       </c>
       <c r="AE70" s="165" t="n">
-        <v>707.2794947404533</v>
+        <v>707.2794947404523</v>
       </c>
       <c r="AF70" s="165" t="n">
-        <v>1000.212466108144</v>
+        <v>1000.212466108143</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>1320.027039893261</v>
+        <v>1320.02703989326</v>
       </c>
       <c r="AH70" s="166" t="n">
-        <v>1686.903562829613</v>
+        <v>1686.903562829614</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" thickBot="1">
@@ -7603,13 +7603,13 @@
         </is>
       </c>
       <c r="C71" s="155" t="n">
-        <v>0.01122430865913447</v>
+        <v>0.01122430865913448</v>
       </c>
       <c r="D71" s="156" t="n">
         <v>0.01686512814045282</v>
       </c>
       <c r="E71" s="156" t="n">
-        <v>0.02293026875728913</v>
+        <v>0.02293026875728912</v>
       </c>
       <c r="F71" s="156" t="n">
         <v>0.02891214347838031</v>
@@ -7618,22 +7618,22 @@
         <v>0.03493993914006312</v>
       </c>
       <c r="H71" s="155" t="n">
-        <v>0.001202013507296027</v>
+        <v>0.001202013507296028</v>
       </c>
       <c r="I71" s="156" t="n">
         <v>0.001876713097151192</v>
       </c>
       <c r="J71" s="156" t="n">
-        <v>0.002659554063444628</v>
+        <v>0.002659554063444627</v>
       </c>
       <c r="K71" s="156" t="n">
-        <v>0.003541035171483904</v>
+        <v>0.003541035171483905</v>
       </c>
       <c r="L71" s="157" t="n">
         <v>0.004539058695875703</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>76.05946338317243</v>
+        <v>76.05946338317248</v>
       </c>
       <c r="N71" s="159" t="n">
         <v>120.2983458350366</v>
@@ -7653,37 +7653,37 @@
         </is>
       </c>
       <c r="T71" s="155" t="n">
-        <v>0.01477718426049838</v>
+        <v>0.01477718426049839</v>
       </c>
       <c r="U71" s="156" t="n">
         <v>0.02220351503836899</v>
       </c>
       <c r="V71" s="156" t="n">
-        <v>0.03018847902881347</v>
+        <v>0.03018847902881346</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>0.03806382063436033</v>
+        <v>0.03806382063436034</v>
       </c>
       <c r="X71" s="157" t="n">
         <v>0.045999618720671</v>
       </c>
       <c r="Y71" s="155" t="n">
-        <v>0.001381881265885539</v>
+        <v>0.00138188126588554</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>0.002158825486588776</v>
+        <v>0.002158825486588777</v>
       </c>
       <c r="AA71" s="156" t="n">
-        <v>0.003061392048896288</v>
+        <v>0.003061392048896286</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>0.004079822765263513</v>
+        <v>0.004079822765263514</v>
       </c>
       <c r="AC71" s="157" t="n">
         <v>0.005235238901162374</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>76.05946338317243</v>
+        <v>76.05946338317248</v>
       </c>
       <c r="AE71" s="159" t="n">
         <v>120.2983458350366</v>
@@ -7708,46 +7708,46 @@
         <v>0.004156074374709216</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.00610363474363276</v>
+        <v>0.006103634743632752</v>
       </c>
       <c r="E72" s="162" t="n">
-        <v>0.008119619452050945</v>
+        <v>0.008119619452050942</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.009972085784422388</v>
+        <v>0.00997208578442238</v>
       </c>
       <c r="G72" s="163" t="n">
-        <v>0.01169742855839976</v>
+        <v>0.01169742855839977</v>
       </c>
       <c r="H72" s="161" t="n">
         <v>0.0003467356301251881</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.0005353512709779978</v>
+        <v>0.0005353512709779972</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.0007495192333084772</v>
+        <v>0.0007495192333084767</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.0009813025103450816</v>
+        <v>0.0009813025103450807</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.001239921512797902</v>
+        <v>0.001239921512797903</v>
       </c>
       <c r="M72" s="164" t="n">
         <v>528.7511693736024</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>827.5778405754899</v>
+        <v>827.5778405754888</v>
       </c>
       <c r="O72" s="165" t="n">
         <v>1172.779589597106</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>1552.43831897958</v>
+        <v>1552.438318979579</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>1989.065020628601</v>
+        <v>1989.065020628602</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7755,31 +7755,31 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>0.004277402209740631</v>
+        <v>0.00427740220974063</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.006280908802263824</v>
+        <v>0.006280908802263815</v>
       </c>
       <c r="V72" s="162" t="n">
-        <v>0.008354505066388832</v>
+        <v>0.008354505066388827</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>0.010259467457535</v>
+        <v>0.01025946745753499</v>
       </c>
       <c r="X72" s="163" t="n">
         <v>0.01203238892621377</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.0004062181296861653</v>
+        <v>0.0004062181296861651</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.0006268775811926828</v>
+        <v>0.0006268775811926821</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.0008771793683576047</v>
+        <v>0.0008771793683576041</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>0.001147564003964397</v>
+        <v>0.001147564003964396</v>
       </c>
       <c r="AC72" s="163" t="n">
         <v>0.001448570462989258</v>
@@ -7788,16 +7788,16 @@
         <v>528.7511693736024</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>827.5778405754899</v>
+        <v>827.5778405754888</v>
       </c>
       <c r="AF72" s="165" t="n">
         <v>1172.779589597106</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>1552.43831897958</v>
+        <v>1552.438318979579</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>1989.065020628601</v>
+        <v>1989.065020628602</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7912,46 +7912,46 @@
         <v>0.004156074374709216</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>0.00610363474363276</v>
+        <v>0.006103634743632752</v>
       </c>
       <c r="E74" s="180" t="n">
-        <v>0.008119619452050945</v>
+        <v>0.008119619452050942</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>0.009972085784422388</v>
+        <v>0.00997208578442238</v>
       </c>
       <c r="G74" s="181" t="n">
-        <v>0.01169742855839976</v>
+        <v>0.01169742855839977</v>
       </c>
       <c r="H74" s="179" t="n">
         <v>0.0003467356301251881</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>0.0005353512709779978</v>
+        <v>0.0005353512709779972</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.0007495192333084772</v>
+        <v>0.0007495192333084767</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.0009813025103450816</v>
+        <v>0.0009813025103450807</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.001239921512797902</v>
+        <v>0.001239921512797903</v>
       </c>
       <c r="M74" s="182" t="n">
         <v>528.7511693736024</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>827.5778405754899</v>
+        <v>827.5778405754888</v>
       </c>
       <c r="O74" s="183" t="n">
         <v>1172.779589597106</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>1552.43831897958</v>
+        <v>1552.438318979579</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>1989.065020628601</v>
+        <v>1989.065020628602</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,31 +7959,31 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>0.004277402209740631</v>
+        <v>0.00427740220974063</v>
       </c>
       <c r="U74" s="186" t="n">
-        <v>0.006280908802263824</v>
+        <v>0.006280908802263815</v>
       </c>
       <c r="V74" s="186" t="n">
-        <v>0.008354505066388832</v>
+        <v>0.008354505066388827</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>0.010259467457535</v>
+        <v>0.01025946745753499</v>
       </c>
       <c r="X74" s="187" t="n">
         <v>0.01203238892621377</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.0004062181296861653</v>
+        <v>0.0004062181296861651</v>
       </c>
       <c r="Z74" s="186" t="n">
-        <v>0.0006268775811926828</v>
+        <v>0.0006268775811926821</v>
       </c>
       <c r="AA74" s="186" t="n">
-        <v>0.0008771793683576047</v>
+        <v>0.0008771793683576041</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>0.001147564003964397</v>
+        <v>0.001147564003964396</v>
       </c>
       <c r="AC74" s="187" t="n">
         <v>0.001448570462989258</v>
@@ -7992,16 +7992,16 @@
         <v>528.7511693736024</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>827.5778405754899</v>
+        <v>827.5778405754888</v>
       </c>
       <c r="AF74" s="189" t="n">
         <v>1172.779589597106</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>1552.43831897958</v>
+        <v>1552.438318979579</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>1989.065020628601</v>
+        <v>1989.065020628602</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>540.7658900778283</v>
+        <v>540.7658900778282</v>
       </c>
       <c r="D79" s="149" t="n">
         <v>591.156380035481</v>
@@ -8272,7 +8272,7 @@
         <v>683.8594162227297</v>
       </c>
       <c r="G79" s="150" t="n">
-        <v>730.1040237956695</v>
+        <v>730.1040237956693</v>
       </c>
       <c r="H79" s="148" t="n">
         <v>46.60942554288957</v>
@@ -8287,7 +8287,7 @@
         <v>70.15991233727149</v>
       </c>
       <c r="L79" s="150" t="n">
-        <v>80.71178307249376</v>
+        <v>80.71178307249373</v>
       </c>
       <c r="M79" s="151" t="n">
         <v>55765810.67012809</v>
@@ -8310,7 +8310,7 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>549.8910860054998</v>
+        <v>549.8910860054997</v>
       </c>
       <c r="U79" s="149" t="n">
         <v>601.1318941917833</v>
@@ -8322,7 +8322,7 @@
         <v>695.3992549487214</v>
       </c>
       <c r="X79" s="150" t="n">
-        <v>742.4242207366378</v>
+        <v>742.4242207366376</v>
       </c>
       <c r="Y79" s="148" t="n">
         <v>56.75855415663893</v>
@@ -8337,7 +8337,7 @@
         <v>85.13525096523726</v>
       </c>
       <c r="AC79" s="150" t="n">
-        <v>97.77184978630247</v>
+        <v>97.77184978630244</v>
       </c>
       <c r="AD79" s="151" t="n">
         <v>55765810.67012809</v>
@@ -8362,7 +8362,7 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>1607.554453379702</v>
+        <v>1607.554453379703</v>
       </c>
       <c r="D80" s="156" t="n">
         <v>1764.932686261068</v>
@@ -8371,7 +8371,7 @@
         <v>1914.694122473068</v>
       </c>
       <c r="F80" s="156" t="n">
-        <v>2045.559435761161</v>
+        <v>2045.559435761162</v>
       </c>
       <c r="G80" s="157" t="n">
         <v>2173.160257120019</v>
@@ -8392,7 +8392,7 @@
         <v>171.3698035388963</v>
       </c>
       <c r="M80" s="158" t="n">
-        <v>27848676.16132199</v>
+        <v>27848676.161322</v>
       </c>
       <c r="N80" s="159" t="n">
         <v>31276854.84995834</v>
@@ -8401,7 +8401,7 @@
         <v>35300042.6721456</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>40275391.3265848</v>
+        <v>40275391.32658481</v>
       </c>
       <c r="Q80" s="160" t="n">
         <v>46429635.41744695</v>
@@ -8421,7 +8421,7 @@
         <v>1944.798419732673</v>
       </c>
       <c r="W80" s="156" t="n">
-        <v>2077.721298375962</v>
+        <v>2077.721298375963</v>
       </c>
       <c r="X80" s="157" t="n">
         <v>2207.328358230918</v>
@@ -8442,7 +8442,7 @@
         <v>172.1253226101957</v>
       </c>
       <c r="AD80" s="158" t="n">
-        <v>27848676.16132199</v>
+        <v>27848676.161322</v>
       </c>
       <c r="AE80" s="159" t="n">
         <v>31276854.84995834</v>
@@ -8451,7 +8451,7 @@
         <v>35300042.6721456</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>40275391.3265848</v>
+        <v>40275391.32658481</v>
       </c>
       <c r="AH80" s="160" t="n">
         <v>46429635.41744695</v>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="C81" s="161" t="n">
-        <v>694.1992632514566</v>
+        <v>694.1992632514565</v>
       </c>
       <c r="D81" s="162" t="n">
         <v>753.0874257612755</v>
@@ -8473,10 +8473,10 @@
         <v>810.1737556474518</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>865.4550835011598</v>
+        <v>865.4550835011599</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>921.1319910551514</v>
+        <v>921.1319910551513</v>
       </c>
       <c r="H81" s="161" t="n">
         <v>57.20501079990375</v>
@@ -8491,7 +8491,7 @@
         <v>84.26337691123091</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>96.68597956787396</v>
+        <v>96.68597956787393</v>
       </c>
       <c r="M81" s="164" t="n">
         <v>83614486.83145009</v>
@@ -8503,7 +8503,7 @@
         <v>110922523.9828324</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>127775668.1137237</v>
+        <v>127775668.1137238</v>
       </c>
       <c r="Q81" s="166" t="n">
         <v>148666010.049729</v>
@@ -8523,10 +8523,10 @@
         <v>823.7193136759794</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>879.9262040859423</v>
+        <v>879.9262040859425</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>936.535118228292</v>
+        <v>936.5351182282918</v>
       </c>
       <c r="Y81" s="161" t="n">
         <v>67.07387296490116</v>
@@ -8538,7 +8538,7 @@
         <v>86.61622377196309</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>98.60405753761181</v>
+        <v>98.60405753761182</v>
       </c>
       <c r="AC81" s="163" t="n">
         <v>113.0191160514357</v>
@@ -8553,7 +8553,7 @@
         <v>110922523.9828324</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>127775668.1137237</v>
+        <v>127775668.1137238</v>
       </c>
       <c r="AH81" s="166" t="n">
         <v>148666010.049729</v>
@@ -8581,7 +8581,7 @@
         <v>2221.98208238261</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>167.7973209421773</v>
+        <v>167.7973209421774</v>
       </c>
       <c r="I82" s="156" t="n">
         <v>191.8935320354627</v>
@@ -8593,7 +8593,7 @@
         <v>250.7012988012275</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>288.658404718119</v>
+        <v>288.6584047181191</v>
       </c>
       <c r="M82" s="158" t="n">
         <v>10617662.87194712</v>
@@ -8602,7 +8602,7 @@
         <v>12300481.36571886</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>14185021.38653858</v>
+        <v>14185021.38653859</v>
       </c>
       <c r="P82" s="159" t="n">
         <v>16454456.59286631</v>
@@ -8622,7 +8622,7 @@
         <v>2270.304891452402</v>
       </c>
       <c r="V82" s="156" t="n">
-        <v>2481.493647184658</v>
+        <v>2481.493647184659</v>
       </c>
       <c r="W82" s="156" t="n">
         <v>2694.875596610401</v>
@@ -8631,7 +8631,7 @@
         <v>2925.31501511877</v>
       </c>
       <c r="Y82" s="155" t="n">
-        <v>192.906296699936</v>
+        <v>192.9062966999361</v>
       </c>
       <c r="Z82" s="156" t="n">
         <v>220.7394664099383</v>
@@ -8643,7 +8643,7 @@
         <v>288.8468531369479</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>332.9315196784915</v>
+        <v>332.9315196784916</v>
       </c>
       <c r="AD82" s="158" t="n">
         <v>10617662.87194712</v>
@@ -8652,7 +8652,7 @@
         <v>12300481.36571886</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>14185021.38653858</v>
+        <v>14185021.38653859</v>
       </c>
       <c r="AG82" s="159" t="n">
         <v>16454456.59286631</v>
@@ -8668,25 +8668,25 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>740.6807688387953</v>
+        <v>740.6807688387952</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>804.1889325360535</v>
+        <v>804.1889325360536</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>866.169285337294</v>
+        <v>866.1692853372944</v>
       </c>
       <c r="F83" s="162" t="n">
         <v>926.4620427672997</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>987.2904828517676</v>
+        <v>987.2904828517674</v>
       </c>
       <c r="H83" s="161" t="n">
         <v>61.79398873796553</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>70.53560463930656</v>
+        <v>70.53560463930657</v>
       </c>
       <c r="J83" s="162" t="n">
         <v>79.9557839496253</v>
@@ -8695,7 +8695,7 @@
         <v>91.1684423861626</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>104.652291993652</v>
+        <v>104.6522919936519</v>
       </c>
       <c r="M83" s="164" t="n">
         <v>94232149.70339721</v>
@@ -8721,7 +8721,7 @@
         <v>762.303383361641</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>827.545807900453</v>
+        <v>827.5458079004529</v>
       </c>
       <c r="V83" s="162" t="n">
         <v>891.2259651371916</v>
@@ -8730,16 +8730,16 @@
         <v>953.1613931019818</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>1015.561925726948</v>
+        <v>1015.561925726947</v>
       </c>
       <c r="Y83" s="161" t="n">
         <v>72.39474790035669</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>82.59472167400371</v>
+        <v>82.59472167400372</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>93.57406847571042</v>
+        <v>93.57406847571043</v>
       </c>
       <c r="AB83" s="162" t="n">
         <v>106.6150566995608</v>
@@ -8872,25 +8872,25 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>740.6807688387953</v>
+        <v>740.6807688387952</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>804.1889325360535</v>
+        <v>804.1889325360536</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>866.169285337294</v>
+        <v>866.1692853372944</v>
       </c>
       <c r="F85" s="180" t="n">
         <v>926.4620427672997</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>987.2904828517676</v>
+        <v>987.2904828517674</v>
       </c>
       <c r="H85" s="179" t="n">
         <v>61.79398873796553</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>70.53560463930656</v>
+        <v>70.53560463930657</v>
       </c>
       <c r="J85" s="180" t="n">
         <v>79.9557839496253</v>
@@ -8899,7 +8899,7 @@
         <v>91.1684423861626</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>104.652291993652</v>
+        <v>104.6522919936519</v>
       </c>
       <c r="M85" s="182" t="n">
         <v>94232149.70339721</v>
@@ -8925,7 +8925,7 @@
         <v>762.303383361641</v>
       </c>
       <c r="U85" s="186" t="n">
-        <v>827.545807900453</v>
+        <v>827.5458079004529</v>
       </c>
       <c r="V85" s="186" t="n">
         <v>891.2259651371916</v>
@@ -8934,16 +8934,16 @@
         <v>953.1613931019818</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>1015.561925726948</v>
+        <v>1015.561925726947</v>
       </c>
       <c r="Y85" s="185" t="n">
         <v>72.39474790035669</v>
       </c>
       <c r="Z85" s="186" t="n">
-        <v>82.59472167400371</v>
+        <v>82.59472167400372</v>
       </c>
       <c r="AA85" s="186" t="n">
-        <v>93.57406847571042</v>
+        <v>93.57406847571043</v>
       </c>
       <c r="AB85" s="186" t="n">
         <v>106.6150566995608</v>
@@ -9642,7 +9642,7 @@
         <v>7132.963641496925</v>
       </c>
       <c r="E93" s="80" t="n">
-        <v>7525.734884119331</v>
+        <v>7525.734884119332</v>
       </c>
       <c r="F93" s="80" t="n">
         <v>8038.535062615124</v>
@@ -9762,7 +9762,7 @@
         <v>135587.7072163942</v>
       </c>
       <c r="E94" s="86" t="n">
-        <v>144437.7530896319</v>
+        <v>144437.7530896318</v>
       </c>
       <c r="F94" s="86" t="n">
         <v>155678.3959284303</v>
@@ -9994,7 +9994,7 @@
         <v>135587.7072163942</v>
       </c>
       <c r="E96" s="133" t="n">
-        <v>144437.7530896319</v>
+        <v>144437.7530896318</v>
       </c>
       <c r="F96" s="133" t="n">
         <v>155678.3959284303</v>
